--- a/data/trans_bre/P19C02-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P19C02-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 15,24</t>
+          <t>-1,41; 14,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 7,62</t>
+          <t>-8,65; 6,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 2,94</t>
+          <t>-12,98; 2,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 6,06</t>
+          <t>-5,6; 6,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 49,47</t>
+          <t>-3,21; 47,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,43; 19,9</t>
+          <t>-19,59; 17,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-24,03; 6,61</t>
+          <t>-24,68; 4,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,91; 11,62</t>
+          <t>-9,64; 12,39</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 7,97</t>
+          <t>-7,91; 8,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 7,11</t>
+          <t>-8,71; 6,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 14,6</t>
+          <t>-1,14; 15,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 10,48</t>
+          <t>-2,52; 10,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,09; 22,6</t>
+          <t>-18,04; 25,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,25; 18,85</t>
+          <t>-19,85; 16,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 40,2</t>
+          <t>-2,8; 41,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 20,5</t>
+          <t>-4,18; 20,08</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 13,13</t>
+          <t>-4,64; 13,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 8,45</t>
+          <t>-5,87; 8,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 14,81</t>
+          <t>-3,36; 16,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,69; 49,97</t>
+          <t>6,73; 47,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,38; 45,96</t>
+          <t>-14,29; 47,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,64; 29,0</t>
+          <t>-17,82; 31,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 51,87</t>
+          <t>-11,0; 55,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,53; 492,17</t>
+          <t>13,77; 475,94</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 10,13</t>
+          <t>0,73; 9,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,52; 15,39</t>
+          <t>6,18; 15,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,16; 13,41</t>
+          <t>3,48; 13,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,01; 37,58</t>
+          <t>6,05; 37,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 46,25</t>
+          <t>2,39; 43,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,26; 69,22</t>
+          <t>22,78; 69,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,22; 47,89</t>
+          <t>10,91; 48,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,42; 96,12</t>
+          <t>14,24; 94,45</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 12,42</t>
+          <t>-0,62; 12,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 11,7</t>
+          <t>1,53; 12,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 7,39</t>
+          <t>-4,92; 7,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 4,98</t>
+          <t>-12,31; 5,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 91,22</t>
+          <t>-3,97; 85,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,25; 70,59</t>
+          <t>6,55; 74,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,62; 26,66</t>
+          <t>-14,05; 26,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-31,13; 14,04</t>
+          <t>-29,19; 14,67</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,0; -0,89</t>
+          <t>-14,13; -0,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 5,01</t>
+          <t>-8,08; 5,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 7,45</t>
+          <t>-6,16; 7,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,13; -1,06</t>
+          <t>-23,22; -0,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-38,83; -3,36</t>
+          <t>-39,24; -2,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-26,37; 23,77</t>
+          <t>-25,94; 22,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,74; 28,59</t>
+          <t>-16,87; 28,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-35,97; -2,41</t>
+          <t>-35,58; -1,02</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 3,05</t>
+          <t>-2,13; 2,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 3,87</t>
+          <t>-1,03; 3,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 4,83</t>
+          <t>-0,17; 5,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,4; 17,89</t>
+          <t>-0,45; 18,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 11,29</t>
+          <t>-7,01; 9,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 13,73</t>
+          <t>-3,43; 13,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 14,48</t>
+          <t>-0,49; 14,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,88; 48,63</t>
+          <t>-0,62; 51,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C02-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P19C02-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>-0,87</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>-1,53%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 14,49</t>
+          <t>-0,48; 14,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 6,62</t>
+          <t>-9,86; 6,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 2,0</t>
+          <t>-12,83; 2,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 6,32</t>
+          <t>-6,53; 5,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 47,24</t>
+          <t>-1,8; 46,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,59; 17,48</t>
+          <t>-22,43; 17,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-24,68; 4,17</t>
+          <t>-24,31; 4,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 12,39</t>
+          <t>-11,02; 9,6</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,08</t>
+          <t>2,85</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 8,68</t>
+          <t>-7,52; 8,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 6,26</t>
+          <t>-8,33; 7,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 15,2</t>
+          <t>-1,51; 14,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 10,48</t>
+          <t>-3,15; 9,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,04; 25,79</t>
+          <t>-17,49; 23,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,85; 16,77</t>
+          <t>-18,64; 19,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 41,71</t>
+          <t>-3,33; 40,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 20,08</t>
+          <t>-5,25; 18,59</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26,37</t>
+          <t>7,61</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>15,6%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 13,05</t>
+          <t>-4,82; 13,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 8,8</t>
+          <t>-5,92; 8,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 16,12</t>
+          <t>-3,71; 15,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,73; 47,86</t>
+          <t>-0,53; 15,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 47,06</t>
+          <t>-13,89; 47,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,82; 31,23</t>
+          <t>-18,67; 30,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 55,59</t>
+          <t>-10,77; 55,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,77; 475,94</t>
+          <t>-1,14; 33,48</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18,42</t>
+          <t>7,73</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>18,9%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 9,78</t>
+          <t>-0,1; 9,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,18; 15,75</t>
+          <t>6,26; 15,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,48; 13,44</t>
+          <t>4,01; 13,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,05; 37,71</t>
+          <t>3,41; 12,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,39; 43,86</t>
+          <t>-0,16; 46,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,78; 69,18</t>
+          <t>24,03; 68,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,91; 48,94</t>
+          <t>12,84; 48,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,24; 94,45</t>
+          <t>7,69; 31,37</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,88</t>
+          <t>5,62</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-4,93%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 12,11</t>
+          <t>-0,64; 12,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 12,16</t>
+          <t>0,75; 12,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 7,73</t>
+          <t>-5,28; 7,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 5,27</t>
+          <t>-0,3; 11,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 85,94</t>
+          <t>-2,6; 88,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,55; 74,79</t>
+          <t>3,11; 73,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,05; 26,93</t>
+          <t>-14,99; 25,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-29,19; 14,67</t>
+          <t>-0,72; 33,9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-11,99</t>
+          <t>-12,98</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-21,92%</t>
+          <t>-22,9%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,13; -0,62</t>
+          <t>-14,35; -1,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 5,07</t>
+          <t>-8,37; 4,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 7,25</t>
+          <t>-5,99; 7,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,22; -0,46</t>
+          <t>-23,53; -1,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-39,24; -2,24</t>
+          <t>-38,45; -3,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-25,94; 22,95</t>
+          <t>-25,66; 21,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,87; 28,23</t>
+          <t>-16,61; 28,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-35,58; -1,02</t>
+          <t>-35,95; -2,24</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,3</t>
+          <t>1,52</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 2,69</t>
+          <t>-2,25; 2,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 3,76</t>
+          <t>-0,93; 3,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 5,1</t>
+          <t>-0,24; 5,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 18,66</t>
+          <t>-0,77; 3,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 9,84</t>
+          <t>-7,62; 10,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 13,24</t>
+          <t>-3,04; 13,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 14,98</t>
+          <t>-0,64; 15,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 51,2</t>
+          <t>-1,61; 8,66</t>
         </is>
       </c>
     </row>
